--- a/ProjectManagement/EvaluationHW2.xlsx
+++ b/ProjectManagement/EvaluationHW2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilkohinrichs/Ultraschallradar_Automatisierungstechnik/ProjectManagement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E856C1C8-3DBB-0348-B8AD-D9E38833554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6417D7-CD4A-B44A-869B-069C0106A30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="600" windowWidth="21800" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -992,7 +992,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,6 +1124,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1223,6 +1229,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1241,7 +1248,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1556,14 +1562,14 @@
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="29"/>
+      <c r="B6" s="23"/>
     </row>
     <row r="7" spans="1:4" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
@@ -1887,7 +1893,7 @@
       <c r="F49" s="8">
         <v>10</v>
       </c>
-      <c r="G49" s="24" t="s">
+      <c r="G49" s="25" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1904,7 +1910,7 @@
       <c r="F50" s="8">
         <v>5</v>
       </c>
-      <c r="G50" s="24"/>
+      <c r="G50" s="25"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="7"/>
@@ -1917,7 +1923,7 @@
       <c r="F51" s="8">
         <v>5</v>
       </c>
-      <c r="G51" s="24"/>
+      <c r="G51" s="25"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="7"/>
@@ -1930,7 +1936,7 @@
       <c r="F52" s="8">
         <v>5</v>
       </c>
-      <c r="G52" s="24"/>
+      <c r="G52" s="25"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="7"/>
@@ -1943,7 +1949,7 @@
       <c r="F53" s="8">
         <v>10</v>
       </c>
-      <c r="G53" s="24"/>
+      <c r="G53" s="25"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="8"/>
@@ -1956,7 +1962,7 @@
       <c r="F54" s="8">
         <v>25</v>
       </c>
-      <c r="G54" s="24"/>
+      <c r="G54" s="25"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="7"/>
@@ -1969,7 +1975,7 @@
       <c r="F55" s="8">
         <v>5</v>
       </c>
-      <c r="G55" s="24"/>
+      <c r="G55" s="25"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
@@ -1982,7 +1988,7 @@
       <c r="F56" s="8">
         <v>5</v>
       </c>
-      <c r="G56" s="24"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
@@ -1995,7 +2001,7 @@
       <c r="F57" s="8">
         <v>10</v>
       </c>
-      <c r="G57" s="24"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="7"/>
@@ -2008,7 +2014,7 @@
       <c r="F58" s="8">
         <v>5</v>
       </c>
-      <c r="G58" s="24"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
@@ -2023,7 +2029,7 @@
       <c r="F59" s="8">
         <v>5</v>
       </c>
-      <c r="G59" s="24"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
@@ -2036,7 +2042,7 @@
       <c r="F60" s="8">
         <v>20</v>
       </c>
-      <c r="G60" s="24"/>
+      <c r="G60" s="25"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="7"/>
@@ -2049,7 +2055,7 @@
       <c r="F61" s="8">
         <v>10</v>
       </c>
-      <c r="G61" s="24"/>
+      <c r="G61" s="25"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="7"/>
@@ -2063,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="8"/>
-      <c r="G62" s="24"/>
+      <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
@@ -2924,7 +2930,7 @@
       <c r="F140" s="8">
         <v>10</v>
       </c>
-      <c r="G140" s="25" t="s">
+      <c r="G140" s="26" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2943,7 +2949,7 @@
       <c r="F141" s="8">
         <v>10</v>
       </c>
-      <c r="G141" s="25"/>
+      <c r="G141" s="26"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="8"/>
@@ -2958,7 +2964,7 @@
       <c r="F142" s="8">
         <v>10</v>
       </c>
-      <c r="G142" s="25"/>
+      <c r="G142" s="26"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8"/>
@@ -2973,7 +2979,7 @@
       <c r="F143" s="8">
         <v>10</v>
       </c>
-      <c r="G143" s="25"/>
+      <c r="G143" s="26"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="7"/>
@@ -2988,7 +2994,7 @@
       <c r="F144" s="8">
         <v>50</v>
       </c>
-      <c r="G144" s="25"/>
+      <c r="G144" s="26"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8"/>
@@ -3005,7 +3011,7 @@
       <c r="F145" s="8">
         <v>30</v>
       </c>
-      <c r="G145" s="25"/>
+      <c r="G145" s="26"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="7"/>
@@ -3020,7 +3026,7 @@
       <c r="F146" s="8">
         <v>40</v>
       </c>
-      <c r="G146" s="25"/>
+      <c r="G146" s="26"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8"/>
@@ -3034,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="F147" s="8"/>
-      <c r="G147" s="25"/>
+      <c r="G147" s="26"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E148">
@@ -3044,10 +3050,10 @@
       <c r="F148">
         <v>170</v>
       </c>
-      <c r="G148" s="25"/>
+      <c r="G148" s="26"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G149" s="25"/>
+      <c r="G149" s="26"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="s">
@@ -3064,7 +3070,7 @@
       <c r="F150" s="8">
         <v>10</v>
       </c>
-      <c r="G150" s="25"/>
+      <c r="G150" s="26"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
@@ -3079,7 +3085,7 @@
       <c r="F151" s="8">
         <v>10</v>
       </c>
-      <c r="G151" s="25"/>
+      <c r="G151" s="26"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="7"/>
@@ -3092,7 +3098,7 @@
       <c r="F152" s="8">
         <v>10</v>
       </c>
-      <c r="G152" s="25"/>
+      <c r="G152" s="26"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="7"/>
@@ -3107,7 +3113,7 @@
       <c r="F153" s="8">
         <v>10</v>
       </c>
-      <c r="G153" s="25"/>
+      <c r="G153" s="26"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="8"/>
@@ -3122,7 +3128,7 @@
       <c r="F154" s="8">
         <v>15</v>
       </c>
-      <c r="G154" s="25"/>
+      <c r="G154" s="26"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="8"/>
@@ -3137,7 +3143,7 @@
       <c r="F155" s="8">
         <v>10</v>
       </c>
-      <c r="G155" s="25"/>
+      <c r="G155" s="26"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="8"/>
@@ -3152,7 +3158,7 @@
       <c r="F156" s="8">
         <v>15</v>
       </c>
-      <c r="G156" s="25"/>
+      <c r="G156" s="26"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="8"/>
@@ -3165,7 +3171,7 @@
       <c r="F157" s="8">
         <v>15</v>
       </c>
-      <c r="G157" s="25"/>
+      <c r="G157" s="26"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="8"/>
@@ -3178,7 +3184,7 @@
       <c r="F158" s="8">
         <v>5</v>
       </c>
-      <c r="G158" s="25"/>
+      <c r="G158" s="26"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="8"/>
@@ -3193,7 +3199,7 @@
       <c r="F159" s="8">
         <v>0</v>
       </c>
-      <c r="G159" s="25"/>
+      <c r="G159" s="26"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="8"/>
@@ -3207,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="F160" s="8"/>
-      <c r="G160" s="25"/>
+      <c r="G160" s="26"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E161">
@@ -3218,10 +3224,10 @@
         <f>SUM(F150:F159)</f>
         <v>100</v>
       </c>
-      <c r="G161" s="25"/>
+      <c r="G161" s="26"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G162" s="25"/>
+      <c r="G162" s="26"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="str">
@@ -3241,7 +3247,7 @@
         <f t="shared" ref="F163:F171" si="1">F150</f>
         <v>10</v>
       </c>
-      <c r="G163" s="25"/>
+      <c r="G163" s="26"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
@@ -3260,7 +3266,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G164" s="25"/>
+      <c r="G164" s="26"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="8"/>
@@ -3277,7 +3283,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G165" s="25"/>
+      <c r="G165" s="26"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="7"/>
@@ -3294,7 +3300,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G166" s="25"/>
+      <c r="G166" s="26"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="7"/>
@@ -3311,7 +3317,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G167" s="25"/>
+      <c r="G167" s="26"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="7"/>
@@ -3326,7 +3332,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G168" s="25"/>
+      <c r="G168" s="26"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="7"/>
@@ -3343,7 +3349,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G169" s="25"/>
+      <c r="G169" s="26"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="8"/>
@@ -3360,7 +3366,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G170" s="25"/>
+      <c r="G170" s="26"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="8"/>
@@ -3375,7 +3381,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G171" s="25"/>
+      <c r="G171" s="26"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="8"/>
@@ -3393,7 +3399,7 @@
         <f t="shared" ref="F172" si="3">F159</f>
         <v>0</v>
       </c>
-      <c r="G172" s="25"/>
+      <c r="G172" s="26"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="8"/>
@@ -3407,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="8"/>
-      <c r="G173" s="25"/>
+      <c r="G173" s="26"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E174">
@@ -3418,7 +3424,7 @@
         <f>SUM(F163:F172)</f>
         <v>100</v>
       </c>
-      <c r="G174" s="25"/>
+      <c r="G174" s="26"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="str">
@@ -3435,7 +3441,7 @@
       <c r="F175" s="8">
         <v>0</v>
       </c>
-      <c r="G175" s="25"/>
+      <c r="G175" s="26"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="7"/>
@@ -3449,7 +3455,7 @@
       <c r="F176" s="8">
         <v>0</v>
       </c>
-      <c r="G176" s="25"/>
+      <c r="G176" s="26"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="7"/>
@@ -3463,7 +3469,7 @@
       <c r="F177" s="8">
         <v>0</v>
       </c>
-      <c r="G177" s="25"/>
+      <c r="G177" s="26"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="7"/>
@@ -3477,7 +3483,7 @@
       <c r="F178" s="8">
         <v>0</v>
       </c>
-      <c r="G178" s="25"/>
+      <c r="G178" s="26"/>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="7"/>
@@ -3491,7 +3497,7 @@
       <c r="F179" s="8">
         <v>0</v>
       </c>
-      <c r="G179" s="25"/>
+      <c r="G179" s="26"/>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="7"/>
@@ -3505,7 +3511,7 @@
       <c r="F180" s="8">
         <v>0</v>
       </c>
-      <c r="G180" s="25"/>
+      <c r="G180" s="26"/>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="7"/>
@@ -3519,7 +3525,7 @@
       <c r="F181" s="8">
         <v>0</v>
       </c>
-      <c r="G181" s="25"/>
+      <c r="G181" s="26"/>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="7"/>
@@ -3533,7 +3539,7 @@
       <c r="F182" s="8">
         <v>0</v>
       </c>
-      <c r="G182" s="25"/>
+      <c r="G182" s="26"/>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="7"/>
@@ -3547,7 +3553,7 @@
       <c r="F183" s="8">
         <v>0</v>
       </c>
-      <c r="G183" s="25"/>
+      <c r="G183" s="26"/>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="7"/>
@@ -3564,7 +3570,7 @@
       <c r="F184" s="8">
         <v>0</v>
       </c>
-      <c r="G184" s="25"/>
+      <c r="G184" s="26"/>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="7"/>
@@ -3578,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="F185" s="8"/>
-      <c r="G185" s="25"/>
+      <c r="G185" s="26"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
@@ -3591,7 +3597,7 @@
         <f>SUM(F175:F184)</f>
         <v>0</v>
       </c>
-      <c r="G186" s="25"/>
+      <c r="G186" s="26"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="s">
@@ -3608,7 +3614,7 @@
       <c r="F187" s="8">
         <v>0</v>
       </c>
-      <c r="G187" s="25"/>
+      <c r="G187" s="26"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="7"/>
@@ -3621,7 +3627,7 @@
       <c r="F188" s="8">
         <v>0</v>
       </c>
-      <c r="G188" s="25"/>
+      <c r="G188" s="26"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="7"/>
@@ -3634,7 +3640,7 @@
       <c r="F189" s="8">
         <v>0</v>
       </c>
-      <c r="G189" s="25"/>
+      <c r="G189" s="26"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="7"/>
@@ -3647,7 +3653,7 @@
       <c r="F190" s="8">
         <v>0</v>
       </c>
-      <c r="G190" s="25"/>
+      <c r="G190" s="26"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="7"/>
@@ -3660,7 +3666,7 @@
       <c r="F191" s="8">
         <v>0</v>
       </c>
-      <c r="G191" s="25"/>
+      <c r="G191" s="26"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="7"/>
@@ -3673,7 +3679,7 @@
       <c r="F192" s="8">
         <v>0</v>
       </c>
-      <c r="G192" s="25"/>
+      <c r="G192" s="26"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" s="7"/>
@@ -3686,7 +3692,7 @@
       <c r="F193" s="8">
         <v>0</v>
       </c>
-      <c r="G193" s="25"/>
+      <c r="G193" s="26"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" s="7"/>
@@ -3703,7 +3709,7 @@
       <c r="F194" s="8">
         <v>0</v>
       </c>
-      <c r="G194" s="25"/>
+      <c r="G194" s="26"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" s="8"/>
@@ -3718,7 +3724,7 @@
       <c r="F195" s="8">
         <v>0</v>
       </c>
-      <c r="G195" s="25"/>
+      <c r="G195" s="26"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" s="8"/>
@@ -3733,7 +3739,7 @@
       <c r="F196" s="8">
         <v>0</v>
       </c>
-      <c r="G196" s="25"/>
+      <c r="G196" s="26"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" s="8"/>
@@ -3748,7 +3754,7 @@
       <c r="F197" s="8">
         <v>0</v>
       </c>
-      <c r="G197" s="25"/>
+      <c r="G197" s="26"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="8"/>
@@ -3762,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="F198" s="8"/>
-      <c r="G198" s="25"/>
+      <c r="G198" s="26"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E199">
@@ -3773,10 +3779,10 @@
         <f>SUM(F187:F197)</f>
         <v>0</v>
       </c>
-      <c r="G199" s="25"/>
+      <c r="G199" s="26"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G200" s="25"/>
+      <c r="G200" s="26"/>
     </row>
     <row r="201" spans="1:12" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
@@ -3915,7 +3921,7 @@
       <c r="F214" s="8">
         <v>5</v>
       </c>
-      <c r="G214" s="26" t="s">
+      <c r="G214" s="27" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3932,7 +3938,7 @@
       <c r="F215" s="8">
         <v>10</v>
       </c>
-      <c r="G215" s="26"/>
+      <c r="G215" s="27"/>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="7"/>
@@ -3945,7 +3951,7 @@
       <c r="F216" s="8">
         <v>10</v>
       </c>
-      <c r="G216" s="26"/>
+      <c r="G216" s="27"/>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="7"/>
@@ -3958,7 +3964,7 @@
       <c r="F217" s="8">
         <v>5</v>
       </c>
-      <c r="G217" s="26"/>
+      <c r="G217" s="27"/>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="7"/>
@@ -3971,7 +3977,7 @@
       <c r="F218" s="8">
         <v>5</v>
       </c>
-      <c r="G218" s="26"/>
+      <c r="G218" s="27"/>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="7"/>
@@ -3984,7 +3990,7 @@
       <c r="F219" s="8">
         <v>5</v>
       </c>
-      <c r="G219" s="26"/>
+      <c r="G219" s="27"/>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="7"/>
@@ -3998,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="F220" s="8"/>
-      <c r="G220" s="26"/>
+      <c r="G220" s="27"/>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
@@ -4011,12 +4017,12 @@
         <f>SUM(F214:F219)</f>
         <v>40</v>
       </c>
-      <c r="G221" s="26"/>
+      <c r="G221" s="27"/>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
-      <c r="G222" s="26"/>
+      <c r="G222" s="27"/>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="7" t="s">
@@ -4031,7 +4037,7 @@
       <c r="F223" s="8">
         <v>5</v>
       </c>
-      <c r="G223" s="26"/>
+      <c r="G223" s="27"/>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="7" t="s">
@@ -4046,7 +4052,7 @@
       <c r="F224" s="8">
         <v>25</v>
       </c>
-      <c r="G224" s="26"/>
+      <c r="G224" s="27"/>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="7"/>
@@ -4059,7 +4065,7 @@
       <c r="F225" s="8">
         <v>15</v>
       </c>
-      <c r="G225" s="26"/>
+      <c r="G225" s="27"/>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="7"/>
@@ -4072,7 +4078,7 @@
       <c r="F226" s="8">
         <v>15</v>
       </c>
-      <c r="G226" s="26"/>
+      <c r="G226" s="27"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="7"/>
@@ -4085,7 +4091,7 @@
       <c r="F227" s="8">
         <v>20</v>
       </c>
-      <c r="G227" s="26"/>
+      <c r="G227" s="27"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="7"/>
@@ -4098,7 +4104,7 @@
       <c r="F228" s="8">
         <v>15</v>
       </c>
-      <c r="G228" s="26"/>
+      <c r="G228" s="27"/>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="7"/>
@@ -4112,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="F229" s="8"/>
-      <c r="G229" s="26"/>
+      <c r="G229" s="27"/>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
@@ -4125,7 +4131,7 @@
         <f>SUM(F223:F228)</f>
         <v>95</v>
       </c>
-      <c r="G230" s="26"/>
+      <c r="G230" s="27"/>
     </row>
     <row r="232" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
@@ -5063,7 +5069,7 @@
       <c r="F316" s="8">
         <v>100</v>
       </c>
-      <c r="H316" s="27" t="s">
+      <c r="H316" s="28" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5078,7 +5084,7 @@
       <c r="F317" s="8">
         <v>100</v>
       </c>
-      <c r="H317" s="27"/>
+      <c r="H317" s="28"/>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="8"/>
@@ -5091,7 +5097,7 @@
       <c r="F318" s="8">
         <v>100</v>
       </c>
-      <c r="H318" s="27"/>
+      <c r="H318" s="28"/>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="8"/>
@@ -5104,7 +5110,7 @@
       <c r="F319" s="8">
         <v>100</v>
       </c>
-      <c r="H319" s="27"/>
+      <c r="H319" s="28"/>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="7" t="s">
@@ -5115,7 +5121,7 @@
       <c r="D320" s="8"/>
       <c r="E320" s="8"/>
       <c r="F320" s="8"/>
-      <c r="H320" s="27"/>
+      <c r="H320" s="28"/>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="7"/>
@@ -5128,7 +5134,7 @@
       <c r="F321" s="8">
         <v>50</v>
       </c>
-      <c r="H321" s="27"/>
+      <c r="H321" s="28"/>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="8"/>
@@ -5143,7 +5149,7 @@
       <c r="F322" s="8">
         <v>0</v>
       </c>
-      <c r="H322" s="27"/>
+      <c r="H322" s="28"/>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="8"/>
@@ -5158,7 +5164,7 @@
       <c r="F323" s="8">
         <v>0</v>
       </c>
-      <c r="H323" s="27"/>
+      <c r="H323" s="28"/>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="8"/>
@@ -5173,7 +5179,7 @@
       <c r="F324" s="8">
         <v>100</v>
       </c>
-      <c r="H324" s="27"/>
+      <c r="H324" s="28"/>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="8"/>
@@ -5182,7 +5188,7 @@
       <c r="D325" s="8"/>
       <c r="E325" s="8"/>
       <c r="F325" s="8"/>
-      <c r="H325" s="27"/>
+      <c r="H325" s="28"/>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="8"/>
@@ -5196,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="F326" s="8"/>
-      <c r="H326" s="27"/>
+      <c r="H326" s="28"/>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E327">
@@ -5207,7 +5213,7 @@
         <f>SUM(F316:F325)</f>
         <v>550</v>
       </c>
-      <c r="H327" s="27"/>
+      <c r="H327" s="28"/>
     </row>
     <row r="328" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A328" s="5" t="s">
@@ -6062,6 +6068,7 @@
     <mergeCell ref="G214:G230"/>
     <mergeCell ref="H316:H327"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B24" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B17" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -6084,12 +6091,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>

--- a/ProjectManagement/EvaluationHW2.xlsx
+++ b/ProjectManagement/EvaluationHW2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/ProjectManagement/EvaluationHW2.xlsx
+++ b/ProjectManagement/EvaluationHW2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilkohinrichs/Ultraschallradar_Automatisierungstechnik/ProjectManagement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6417D7-CD4A-B44A-869B-069C0106A30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D808D47E-3647-9D44-A02D-18B7E47C6E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,23 +48,55 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Segoe UI"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>Elmar Wings:</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Segoe UI"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-main page
-descriptions of the functions
-descriptions of the parameters
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">main page
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">descriptions of the functions
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">descriptions of the parameters
 </t>
         </r>
       </text>
@@ -75,25 +107,77 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Segoe UI"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>Elmar Wings:</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Segoe UI"/>
             <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-in all possible files:
-- py
-- tex
--bib
-- ...</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">in all possible files:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- py
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- tex
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">-bib
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>- ...</t>
         </r>
       </text>
     </comment>
@@ -694,9 +778,6 @@
     <t>Idee/Struktur</t>
   </si>
   <si>
-    <t>z.B. nRF Connect</t>
-  </si>
-  <si>
     <t>Test des kompletten Systems</t>
   </si>
   <si>
@@ -964,9 +1045,6 @@
     <t>Ultraschallradar</t>
   </si>
   <si>
-    <t>Das Projekt umfasst die Entwicklung und Realisierung eines autonomen Radarsystems zur digitalen Umfelderfassung. Als zentrale Steuerungseinheit dient der Mikrocontroller Arduino Nano 33 BLE Sense Lite.</t>
-  </si>
-  <si>
     <t>Hinrichs</t>
   </si>
   <si>
@@ -983,6 +1061,12 @@
   </si>
   <si>
     <t>WH171</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>Das Projekt umfasst die Entwicklung und Realisierung eines autonomen Radarsystems zur digitalen Umfelderfassung. Als zentrale Steuerungseinheit dient der Mikrocontroller Arduino Nano 33 BLE Sense.</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1076,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1129,6 +1213,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1555,7 +1654,7 @@
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1566,7 +1665,7 @@
     </row>
     <row r="7" spans="1:4" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="24" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
@@ -1592,30 +1691,30 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C12" s="1">
         <v>7026413</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C13" s="1">
         <v>7025823</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -2907,7 +3006,7 @@
         <v>91</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8" t="s">
@@ -2921,7 +3020,7 @@
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8" t="s">
@@ -3074,7 +3173,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B151" s="8"/>
       <c r="C151" s="8" t="s">
@@ -3251,7 +3350,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8" t="str">
@@ -3715,7 +3814,7 @@
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D195" s="8"/>
       <c r="E195" s="8" t="s">
@@ -3905,7 +4004,7 @@
     </row>
     <row r="213" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
@@ -4041,7 +4140,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="7" t="s">
-        <v>186</v>
+        <v>281</v>
       </c>
       <c r="B224" s="7"/>
       <c r="C224" s="8" t="s">
@@ -4135,7 +4234,7 @@
     </row>
     <row r="232" spans="1:7" ht="19" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -4382,7 +4481,7 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" s="7" t="s">
-        <v>186</v>
+        <v>281</v>
       </c>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="s">
@@ -4581,11 +4680,11 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A273" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B273" s="7"/>
       <c r="C273" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D273" s="8"/>
       <c r="E273" s="8" t="s">
@@ -4599,7 +4698,7 @@
       <c r="A274" s="8"/>
       <c r="B274" s="8"/>
       <c r="C274" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D274" s="8"/>
       <c r="E274" s="8"/>
@@ -4611,7 +4710,7 @@
       <c r="A275" s="7"/>
       <c r="B275" s="8"/>
       <c r="C275" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D275" s="8"/>
       <c r="E275" s="8"/>
@@ -4623,7 +4722,7 @@
       <c r="A276" s="8"/>
       <c r="B276" s="8"/>
       <c r="C276" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D276" s="8"/>
       <c r="E276" s="8" t="s">
@@ -4637,7 +4736,7 @@
       <c r="A277" s="8"/>
       <c r="B277" s="8"/>
       <c r="C277" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D277" s="8"/>
       <c r="E277" s="8" t="s">
@@ -4651,7 +4750,7 @@
       <c r="A278" s="7"/>
       <c r="B278" s="8"/>
       <c r="C278" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D278" s="8"/>
       <c r="E278" s="8" t="s">
@@ -4665,7 +4764,7 @@
       <c r="A279" s="7"/>
       <c r="B279" s="8"/>
       <c r="C279" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D279" s="8"/>
       <c r="E279" s="8" t="s">
@@ -4710,17 +4809,17 @@
     </row>
     <row r="285" spans="1:12" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K285"/>
       <c r="L285"/>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A286" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B286" s="8" t="s">
         <v>196</v>
-      </c>
-      <c r="B286" s="8" t="s">
-        <v>197</v>
       </c>
       <c r="C286" s="8" t="s">
         <v>4</v>
@@ -4765,7 +4864,7 @@
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D289" s="8"/>
       <c r="E289" s="8">
@@ -4779,7 +4878,7 @@
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D290" s="8"/>
       <c r="E290" s="8">
@@ -4832,7 +4931,7 @@
       </c>
       <c r="B294" s="7"/>
       <c r="C294" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D294" s="8"/>
       <c r="E294" s="8"/>
@@ -4900,12 +4999,12 @@
     </row>
     <row r="302" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A302" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B303" s="8" t="s">
         <v>87</v>
@@ -4920,7 +5019,7 @@
     <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304" s="7"/>
       <c r="B304" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C304" s="8"/>
       <c r="D304" s="8"/>
@@ -4932,7 +5031,7 @@
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="7"/>
       <c r="B305" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C305" s="8"/>
       <c r="D305" s="8"/>
@@ -4944,10 +5043,10 @@
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="7"/>
       <c r="B306" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C306" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="C306" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="D306" s="8"/>
       <c r="E306" s="8"/>
@@ -4973,7 +5072,7 @@
         <v>104</v>
       </c>
       <c r="C308" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D308" s="8"/>
       <c r="E308" s="8"/>
@@ -4985,7 +5084,7 @@
       <c r="A309" s="7"/>
       <c r="B309" s="8"/>
       <c r="C309" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D309" s="8"/>
       <c r="E309" s="8"/>
@@ -4997,7 +5096,7 @@
       <c r="A310" s="7"/>
       <c r="B310" s="8"/>
       <c r="C310" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D310" s="8"/>
       <c r="E310" s="8"/>
@@ -5009,7 +5108,7 @@
       <c r="A311" s="7"/>
       <c r="B311" s="8"/>
       <c r="C311" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D311" s="8"/>
       <c r="E311" s="8"/>
@@ -5058,10 +5157,10 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B316" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B316" s="8" t="s">
-        <v>211</v>
       </c>
       <c r="C316" s="8"/>
       <c r="D316" s="8"/>
@@ -5076,7 +5175,7 @@
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="8"/>
       <c r="B317" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C317" s="8"/>
       <c r="D317" s="8"/>
@@ -5089,7 +5188,7 @@
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="8"/>
       <c r="B318" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C318" s="8"/>
       <c r="D318" s="8"/>
@@ -5102,7 +5201,7 @@
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="8"/>
       <c r="B319" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C319" s="8"/>
       <c r="D319" s="8"/>
@@ -5114,7 +5213,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B320" s="8"/>
       <c r="C320" s="8"/>
@@ -5126,7 +5225,7 @@
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="7"/>
       <c r="B321" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C321" s="8"/>
       <c r="D321" s="8"/>
@@ -5139,7 +5238,7 @@
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="8"/>
       <c r="B322" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C322" s="8"/>
       <c r="D322" s="8"/>
@@ -5154,7 +5253,7 @@
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="8"/>
       <c r="B323" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C323" s="8"/>
       <c r="D323" s="8"/>
@@ -5169,7 +5268,7 @@
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="8"/>
       <c r="B324" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C324" s="8"/>
       <c r="D324" s="8"/>
@@ -5265,7 +5364,7 @@
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="8"/>
       <c r="B332" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C332" s="8"/>
       <c r="D332" s="8"/>
@@ -5279,7 +5378,7 @@
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="8"/>
       <c r="B333" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C333" s="8"/>
       <c r="D333" s="8"/>
@@ -5291,7 +5390,7 @@
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="8"/>
       <c r="B334" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C334" s="8"/>
       <c r="D334" s="8"/>
@@ -5305,7 +5404,7 @@
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="8"/>
       <c r="B335" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C335" s="8"/>
       <c r="D335" s="8"/>
@@ -5317,7 +5416,7 @@
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="8"/>
       <c r="B336" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C336" s="8"/>
       <c r="D336" s="8"/>
@@ -5438,10 +5537,10 @@
       </c>
       <c r="B346" s="7"/>
       <c r="C346" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D346" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E346" s="8">
         <v>-20</v>
@@ -5455,7 +5554,7 @@
       <c r="B347" s="7"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E347" s="8">
         <v>-20</v>
@@ -5469,7 +5568,7 @@
       <c r="B348" s="7"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E348" s="8">
         <v>-20</v>
@@ -5482,10 +5581,10 @@
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
       <c r="C349" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E349" s="8">
         <v>-20</v>
@@ -5498,10 +5597,10 @@
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
       <c r="C350" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D350" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E350" s="8">
         <v>-20</v>
@@ -5515,7 +5614,7 @@
       <c r="B351" s="7"/>
       <c r="C351" s="8"/>
       <c r="D351" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E351" s="8">
         <v>-20</v>
@@ -5529,7 +5628,7 @@
       <c r="B352" s="7"/>
       <c r="C352" s="8"/>
       <c r="D352" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E352" s="8">
         <v>-20</v>
@@ -5543,7 +5642,7 @@
       <c r="B353" s="7"/>
       <c r="C353" s="8"/>
       <c r="D353" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E353" s="8">
         <v>0</v>
@@ -5564,7 +5663,7 @@
     </row>
     <row r="355" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A355" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
@@ -5587,7 +5686,7 @@
       <c r="A357" s="7"/>
       <c r="B357" s="8"/>
       <c r="C357" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D357" s="8"/>
       <c r="E357" s="8"/>
@@ -5613,7 +5712,7 @@
       <c r="A359" s="8"/>
       <c r="B359" s="8"/>
       <c r="C359" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D359" s="8"/>
       <c r="E359" s="8"/>
@@ -5637,7 +5736,7 @@
       <c r="A361" s="8"/>
       <c r="B361" s="8"/>
       <c r="C361" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D361" s="8"/>
       <c r="E361" s="8"/>
@@ -5681,15 +5780,15 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B366" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C366" s="8"/>
       <c r="D366" s="8"/>
@@ -5702,7 +5801,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B367" s="8" t="s">
         <v>91</v>
@@ -5722,7 +5821,7 @@
       <c r="A368" s="7"/>
       <c r="B368" s="8"/>
       <c r="C368" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D368" s="8"/>
       <c r="E368" s="8">
@@ -5886,7 +5985,7 @@
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="7"/>
       <c r="B387" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E387">
         <f>E382+E370+E364+E354+E345+E338+E327+E314+E299+E293+E281+E272+E251+E230+E221+E211+E199+E186+E174+E161+E148+E136+E130+E119+E111+E103+E95+E84+E73+E63+E46</f>
@@ -5904,7 +6003,7 @@
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="9"/>
       <c r="B388" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H388" s="13">
         <f>(E388+E387)/(F388+F387)</f>
@@ -5914,7 +6013,7 @@
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="10"/>
       <c r="B389" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H389" s="13">
         <f>(E389+E387)/(F389+F387)</f>
@@ -5924,7 +6023,7 @@
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="11"/>
       <c r="B390" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H390" s="13">
         <f>(E390+E387)/(F390+F387)</f>
@@ -5934,7 +6033,7 @@
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="20"/>
       <c r="B391" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H391" s="13">
         <f>(E391+E387)/(F391+F387)</f>
@@ -5944,7 +6043,7 @@
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="22"/>
       <c r="B392" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H392" s="13">
         <f>(E392+E387)/(F392+F387)</f>
@@ -5953,10 +6052,10 @@
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F394" t="s">
+        <v>251</v>
+      </c>
+      <c r="G394" t="s">
         <v>252</v>
-      </c>
-      <c r="G394" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
@@ -6057,7 +6156,7 @@
     </row>
     <row r="406" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E406" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -6103,7 +6202,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D4" s="14">
         <v>-1</v>
@@ -6119,7 +6218,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D6" s="14">
         <v>-0.5</v>
@@ -6127,7 +6226,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D7" s="14">
         <v>-0.5</v>
@@ -6135,7 +6234,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D8" s="14">
         <v>-1</v>
@@ -6143,7 +6242,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D9" s="14">
         <v>-1</v>
@@ -6151,7 +6250,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D10" s="14">
         <v>-0.5</v>
@@ -6159,7 +6258,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D11" s="14">
         <v>-0.5</v>
@@ -6167,7 +6266,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D12" s="14">
         <v>-0.5</v>
@@ -6175,7 +6274,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D13" s="14">
         <v>-0.5</v>
@@ -6183,7 +6282,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D14" s="14">
         <v>-1</v>
@@ -6191,7 +6290,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D15" s="14">
         <v>-0.3</v>
@@ -6199,7 +6298,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D16" s="14">
         <v>-1</v>
@@ -6207,7 +6306,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D17" s="14">
         <v>-0.2</v>
@@ -6215,7 +6314,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D18" s="14">
         <v>-1</v>
